--- a/Documentation_Reviews.xlsx
+++ b/Documentation_Reviews.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\Bulgaria\SAR-SHIP-DETECTION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF12E2F-0DCE-491C-9EBD-F83E4D8F0587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16CB6E8-D34C-4A35-B368-CCB0CD6184F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1344,7 +1344,7 @@
       <c r="G7" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="36"/>
+      <c r="H7" s="33"/>
     </row>
     <row r="8" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
@@ -3171,6 +3171,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="792da008-023a-4535-b591-94dc32feb87f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="59f62bbe-2e25-4bbc-b3d9-76ec598ebb22">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Документ" ma:contentTypeID="0x0101001E7552FD7427C94D9C1A260AEB17A6B2" ma:contentTypeVersion="12" ma:contentTypeDescription="Създаване на нов документ" ma:contentTypeScope="" ma:versionID="0eee8f92f0c94def16b607033ad67c14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="59f62bbe-2e25-4bbc-b3d9-76ec598ebb22" xmlns:ns3="792da008-023a-4535-b591-94dc32feb87f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e010399ec5a0039dffbd72877db4027a" ns2:_="" ns3:_="">
     <xsd:import namespace="59f62bbe-2e25-4bbc-b3d9-76ec598ebb22"/>
@@ -3371,27 +3391,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="792da008-023a-4535-b591-94dc32feb87f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="59f62bbe-2e25-4bbc-b3d9-76ec598ebb22">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82C94B59-D9CD-4A46-8C75-200A25FAC562}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFF8897D-8941-4075-871C-026DCF83A309}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="792da008-023a-4535-b591-94dc32feb87f"/>
+    <ds:schemaRef ds:uri="59f62bbe-2e25-4bbc-b3d9-76ec598ebb22"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B061121-2C63-4293-B0DE-220AEF1680EF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3410,25 +3429,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFF8897D-8941-4075-871C-026DCF83A309}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="792da008-023a-4535-b591-94dc32feb87f"/>
-    <ds:schemaRef ds:uri="59f62bbe-2e25-4bbc-b3d9-76ec598ebb22"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82C94B59-D9CD-4A46-8C75-200A25FAC562}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{4a18cb8b-b568-4ac9-8854-51740db0235a}" enabled="1" method="Standard" siteId="{60c58ca1-7962-4dfa-8d08-86343a279fd6}" removed="0"/>

--- a/Documentation_Reviews.xlsx
+++ b/Documentation_Reviews.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\Bulgaria\SAR-SHIP-DETECTION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16CB6E8-D34C-4A35-B368-CCB0CD6184F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234D3E0E-ADE7-4617-80FE-7BE75D422855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3171,26 +3171,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="792da008-023a-4535-b591-94dc32feb87f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="59f62bbe-2e25-4bbc-b3d9-76ec598ebb22">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Документ" ma:contentTypeID="0x0101001E7552FD7427C94D9C1A260AEB17A6B2" ma:contentTypeVersion="12" ma:contentTypeDescription="Създаване на нов документ" ma:contentTypeScope="" ma:versionID="0eee8f92f0c94def16b607033ad67c14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="59f62bbe-2e25-4bbc-b3d9-76ec598ebb22" xmlns:ns3="792da008-023a-4535-b591-94dc32feb87f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e010399ec5a0039dffbd72877db4027a" ns2:_="" ns3:_="">
     <xsd:import namespace="59f62bbe-2e25-4bbc-b3d9-76ec598ebb22"/>
@@ -3391,26 +3371,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82C94B59-D9CD-4A46-8C75-200A25FAC562}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="792da008-023a-4535-b591-94dc32feb87f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="59f62bbe-2e25-4bbc-b3d9-76ec598ebb22">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFF8897D-8941-4075-871C-026DCF83A309}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="792da008-023a-4535-b591-94dc32feb87f"/>
-    <ds:schemaRef ds:uri="59f62bbe-2e25-4bbc-b3d9-76ec598ebb22"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B061121-2C63-4293-B0DE-220AEF1680EF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3429,6 +3410,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFF8897D-8941-4075-871C-026DCF83A309}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="792da008-023a-4535-b591-94dc32feb87f"/>
+    <ds:schemaRef ds:uri="59f62bbe-2e25-4bbc-b3d9-76ec598ebb22"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82C94B59-D9CD-4A46-8C75-200A25FAC562}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{4a18cb8b-b568-4ac9-8854-51740db0235a}" enabled="1" method="Standard" siteId="{60c58ca1-7962-4dfa-8d08-86343a279fd6}" removed="0"/>
